--- a/products/trial-00_teacher-command-center/Teacher_Command_Center_Sample.xlsx
+++ b/products/trial-00_teacher-command-center/Teacher_Command_Center_Sample.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setup" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pacing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gradebook" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Standings" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Report" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Setup" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Roster" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pacing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assignments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gradebook" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Standings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Student Report" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Student Report'!$A$1:$H$74</definedName>
@@ -479,7 +479,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <font>
         <b val="1"/>
@@ -527,6 +527,17 @@
         <i val="1"/>
         <color rgb="008A949B"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="007A1A10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8B4AC"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -631,7 +642,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -646,10 +657,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="17495A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -697,7 +708,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <plotArea>
@@ -709,7 +720,7 @@
             <v>Students</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -718,10 +729,10 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C8501A"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:solidFill>
                   <a:srgbClr val="C8501A"/>
                 </a:solidFill>
@@ -755,8 +766,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -784,8 +795,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -809,7 +820,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -819,10 +830,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="3F7F92"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -870,7 +881,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -885,9 +896,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -907,9 +918,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -929,9 +940,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1314,7 +1325,7 @@
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>5.  Gradebook: enter scores. Type M for missing, EX for excused. Past-due blanks count as missing.</t>
+          <t>5.  Gradebook: enter scores. Type M for missing, EX for excused. Past-due blanks count as missing. A score below 0, above the points possible, or any other text turns red.</t>
         </is>
       </c>
     </row>
@@ -13623,17 +13634,20 @@
     <cfRule type="expression" priority="2" dxfId="5">
       <formula>UPPER(M10)="EX"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="6">
+    <cfRule type="expression" priority="3" dxfId="6" stopIfTrue="1">
+      <formula>OR(AND(ISNUMBER(M10),OR(M10&lt;0,AND(M$7&gt;0,M10&gt;M$7))),AND(ISTEXT(M10),UPPER(M10)&lt;&gt;"M",UPPER(M10)&lt;&gt;"EX"))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="7">
       <formula>AND(M10="",M$8=1,$B10&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10:D49">
-    <cfRule type="expression" priority="4" dxfId="7">
+    <cfRule type="expression" priority="5" dxfId="8">
       <formula>AND(ISNUMBER($C10),$C10&lt;$C$3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E49">
-    <cfRule type="expression" priority="5" dxfId="7">
+    <cfRule type="expression" priority="6" dxfId="8">
       <formula>AND(ISNUMBER($E10),$E10&lt;$E$3)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13841,7 +13855,7 @@
         <v/>
       </c>
       <c r="F8" s="58">
-        <f>IF(B8="","",IF(AND(NOT(ISNUMBER(C8)),NOT(ISNUMBER(D8))),"",(IF(ISNUMBER(C8),Setup!$B$22*C8,0)+IF(ISNUMBER(D8),Setup!$B$23*D8,0))/(IF(ISNUMBER(C8),Setup!$B$22,0)+IF(ISNUMBER(D8),Setup!$B$23,0))))</f>
+        <f>IF(B8="","",IF(AND(NOT(ISNUMBER(C8)),NOT(ISNUMBER(D8))),"",ROUND((IF(ISNUMBER(C8),Setup!$B$22*C8,0)+IF(ISNUMBER(D8),Setup!$B$23*D8,0))/(IF(ISNUMBER(C8),Setup!$B$22,0)+IF(ISNUMBER(D8),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G8" s="34">
@@ -13910,7 +13924,7 @@
         <v/>
       </c>
       <c r="F9" s="58">
-        <f>IF(B9="","",IF(AND(NOT(ISNUMBER(C9)),NOT(ISNUMBER(D9))),"",(IF(ISNUMBER(C9),Setup!$B$22*C9,0)+IF(ISNUMBER(D9),Setup!$B$23*D9,0))/(IF(ISNUMBER(C9),Setup!$B$22,0)+IF(ISNUMBER(D9),Setup!$B$23,0))))</f>
+        <f>IF(B9="","",IF(AND(NOT(ISNUMBER(C9)),NOT(ISNUMBER(D9))),"",ROUND((IF(ISNUMBER(C9),Setup!$B$22*C9,0)+IF(ISNUMBER(D9),Setup!$B$23*D9,0))/(IF(ISNUMBER(C9),Setup!$B$22,0)+IF(ISNUMBER(D9),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G9" s="34">
@@ -13979,7 +13993,7 @@
         <v/>
       </c>
       <c r="F10" s="58">
-        <f>IF(B10="","",IF(AND(NOT(ISNUMBER(C10)),NOT(ISNUMBER(D10))),"",(IF(ISNUMBER(C10),Setup!$B$22*C10,0)+IF(ISNUMBER(D10),Setup!$B$23*D10,0))/(IF(ISNUMBER(C10),Setup!$B$22,0)+IF(ISNUMBER(D10),Setup!$B$23,0))))</f>
+        <f>IF(B10="","",IF(AND(NOT(ISNUMBER(C10)),NOT(ISNUMBER(D10))),"",ROUND((IF(ISNUMBER(C10),Setup!$B$22*C10,0)+IF(ISNUMBER(D10),Setup!$B$23*D10,0))/(IF(ISNUMBER(C10),Setup!$B$22,0)+IF(ISNUMBER(D10),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G10" s="34">
@@ -14048,7 +14062,7 @@
         <v/>
       </c>
       <c r="F11" s="58">
-        <f>IF(B11="","",IF(AND(NOT(ISNUMBER(C11)),NOT(ISNUMBER(D11))),"",(IF(ISNUMBER(C11),Setup!$B$22*C11,0)+IF(ISNUMBER(D11),Setup!$B$23*D11,0))/(IF(ISNUMBER(C11),Setup!$B$22,0)+IF(ISNUMBER(D11),Setup!$B$23,0))))</f>
+        <f>IF(B11="","",IF(AND(NOT(ISNUMBER(C11)),NOT(ISNUMBER(D11))),"",ROUND((IF(ISNUMBER(C11),Setup!$B$22*C11,0)+IF(ISNUMBER(D11),Setup!$B$23*D11,0))/(IF(ISNUMBER(C11),Setup!$B$22,0)+IF(ISNUMBER(D11),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G11" s="34">
@@ -14117,7 +14131,7 @@
         <v/>
       </c>
       <c r="F12" s="58">
-        <f>IF(B12="","",IF(AND(NOT(ISNUMBER(C12)),NOT(ISNUMBER(D12))),"",(IF(ISNUMBER(C12),Setup!$B$22*C12,0)+IF(ISNUMBER(D12),Setup!$B$23*D12,0))/(IF(ISNUMBER(C12),Setup!$B$22,0)+IF(ISNUMBER(D12),Setup!$B$23,0))))</f>
+        <f>IF(B12="","",IF(AND(NOT(ISNUMBER(C12)),NOT(ISNUMBER(D12))),"",ROUND((IF(ISNUMBER(C12),Setup!$B$22*C12,0)+IF(ISNUMBER(D12),Setup!$B$23*D12,0))/(IF(ISNUMBER(C12),Setup!$B$22,0)+IF(ISNUMBER(D12),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G12" s="34">
@@ -14186,7 +14200,7 @@
         <v/>
       </c>
       <c r="F13" s="58">
-        <f>IF(B13="","",IF(AND(NOT(ISNUMBER(C13)),NOT(ISNUMBER(D13))),"",(IF(ISNUMBER(C13),Setup!$B$22*C13,0)+IF(ISNUMBER(D13),Setup!$B$23*D13,0))/(IF(ISNUMBER(C13),Setup!$B$22,0)+IF(ISNUMBER(D13),Setup!$B$23,0))))</f>
+        <f>IF(B13="","",IF(AND(NOT(ISNUMBER(C13)),NOT(ISNUMBER(D13))),"",ROUND((IF(ISNUMBER(C13),Setup!$B$22*C13,0)+IF(ISNUMBER(D13),Setup!$B$23*D13,0))/(IF(ISNUMBER(C13),Setup!$B$22,0)+IF(ISNUMBER(D13),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G13" s="34">
@@ -14255,7 +14269,7 @@
         <v/>
       </c>
       <c r="F14" s="58">
-        <f>IF(B14="","",IF(AND(NOT(ISNUMBER(C14)),NOT(ISNUMBER(D14))),"",(IF(ISNUMBER(C14),Setup!$B$22*C14,0)+IF(ISNUMBER(D14),Setup!$B$23*D14,0))/(IF(ISNUMBER(C14),Setup!$B$22,0)+IF(ISNUMBER(D14),Setup!$B$23,0))))</f>
+        <f>IF(B14="","",IF(AND(NOT(ISNUMBER(C14)),NOT(ISNUMBER(D14))),"",ROUND((IF(ISNUMBER(C14),Setup!$B$22*C14,0)+IF(ISNUMBER(D14),Setup!$B$23*D14,0))/(IF(ISNUMBER(C14),Setup!$B$22,0)+IF(ISNUMBER(D14),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G14" s="34">
@@ -14324,7 +14338,7 @@
         <v/>
       </c>
       <c r="F15" s="58">
-        <f>IF(B15="","",IF(AND(NOT(ISNUMBER(C15)),NOT(ISNUMBER(D15))),"",(IF(ISNUMBER(C15),Setup!$B$22*C15,0)+IF(ISNUMBER(D15),Setup!$B$23*D15,0))/(IF(ISNUMBER(C15),Setup!$B$22,0)+IF(ISNUMBER(D15),Setup!$B$23,0))))</f>
+        <f>IF(B15="","",IF(AND(NOT(ISNUMBER(C15)),NOT(ISNUMBER(D15))),"",ROUND((IF(ISNUMBER(C15),Setup!$B$22*C15,0)+IF(ISNUMBER(D15),Setup!$B$23*D15,0))/(IF(ISNUMBER(C15),Setup!$B$22,0)+IF(ISNUMBER(D15),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G15" s="34">
@@ -14393,7 +14407,7 @@
         <v/>
       </c>
       <c r="F16" s="58">
-        <f>IF(B16="","",IF(AND(NOT(ISNUMBER(C16)),NOT(ISNUMBER(D16))),"",(IF(ISNUMBER(C16),Setup!$B$22*C16,0)+IF(ISNUMBER(D16),Setup!$B$23*D16,0))/(IF(ISNUMBER(C16),Setup!$B$22,0)+IF(ISNUMBER(D16),Setup!$B$23,0))))</f>
+        <f>IF(B16="","",IF(AND(NOT(ISNUMBER(C16)),NOT(ISNUMBER(D16))),"",ROUND((IF(ISNUMBER(C16),Setup!$B$22*C16,0)+IF(ISNUMBER(D16),Setup!$B$23*D16,0))/(IF(ISNUMBER(C16),Setup!$B$22,0)+IF(ISNUMBER(D16),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G16" s="34">
@@ -14462,7 +14476,7 @@
         <v/>
       </c>
       <c r="F17" s="58">
-        <f>IF(B17="","",IF(AND(NOT(ISNUMBER(C17)),NOT(ISNUMBER(D17))),"",(IF(ISNUMBER(C17),Setup!$B$22*C17,0)+IF(ISNUMBER(D17),Setup!$B$23*D17,0))/(IF(ISNUMBER(C17),Setup!$B$22,0)+IF(ISNUMBER(D17),Setup!$B$23,0))))</f>
+        <f>IF(B17="","",IF(AND(NOT(ISNUMBER(C17)),NOT(ISNUMBER(D17))),"",ROUND((IF(ISNUMBER(C17),Setup!$B$22*C17,0)+IF(ISNUMBER(D17),Setup!$B$23*D17,0))/(IF(ISNUMBER(C17),Setup!$B$22,0)+IF(ISNUMBER(D17),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G17" s="34">
@@ -14531,7 +14545,7 @@
         <v/>
       </c>
       <c r="F18" s="58">
-        <f>IF(B18="","",IF(AND(NOT(ISNUMBER(C18)),NOT(ISNUMBER(D18))),"",(IF(ISNUMBER(C18),Setup!$B$22*C18,0)+IF(ISNUMBER(D18),Setup!$B$23*D18,0))/(IF(ISNUMBER(C18),Setup!$B$22,0)+IF(ISNUMBER(D18),Setup!$B$23,0))))</f>
+        <f>IF(B18="","",IF(AND(NOT(ISNUMBER(C18)),NOT(ISNUMBER(D18))),"",ROUND((IF(ISNUMBER(C18),Setup!$B$22*C18,0)+IF(ISNUMBER(D18),Setup!$B$23*D18,0))/(IF(ISNUMBER(C18),Setup!$B$22,0)+IF(ISNUMBER(D18),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G18" s="34">
@@ -14600,7 +14614,7 @@
         <v/>
       </c>
       <c r="F19" s="58">
-        <f>IF(B19="","",IF(AND(NOT(ISNUMBER(C19)),NOT(ISNUMBER(D19))),"",(IF(ISNUMBER(C19),Setup!$B$22*C19,0)+IF(ISNUMBER(D19),Setup!$B$23*D19,0))/(IF(ISNUMBER(C19),Setup!$B$22,0)+IF(ISNUMBER(D19),Setup!$B$23,0))))</f>
+        <f>IF(B19="","",IF(AND(NOT(ISNUMBER(C19)),NOT(ISNUMBER(D19))),"",ROUND((IF(ISNUMBER(C19),Setup!$B$22*C19,0)+IF(ISNUMBER(D19),Setup!$B$23*D19,0))/(IF(ISNUMBER(C19),Setup!$B$22,0)+IF(ISNUMBER(D19),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G19" s="34">
@@ -14669,7 +14683,7 @@
         <v/>
       </c>
       <c r="F20" s="58">
-        <f>IF(B20="","",IF(AND(NOT(ISNUMBER(C20)),NOT(ISNUMBER(D20))),"",(IF(ISNUMBER(C20),Setup!$B$22*C20,0)+IF(ISNUMBER(D20),Setup!$B$23*D20,0))/(IF(ISNUMBER(C20),Setup!$B$22,0)+IF(ISNUMBER(D20),Setup!$B$23,0))))</f>
+        <f>IF(B20="","",IF(AND(NOT(ISNUMBER(C20)),NOT(ISNUMBER(D20))),"",ROUND((IF(ISNUMBER(C20),Setup!$B$22*C20,0)+IF(ISNUMBER(D20),Setup!$B$23*D20,0))/(IF(ISNUMBER(C20),Setup!$B$22,0)+IF(ISNUMBER(D20),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G20" s="34">
@@ -14738,7 +14752,7 @@
         <v/>
       </c>
       <c r="F21" s="58">
-        <f>IF(B21="","",IF(AND(NOT(ISNUMBER(C21)),NOT(ISNUMBER(D21))),"",(IF(ISNUMBER(C21),Setup!$B$22*C21,0)+IF(ISNUMBER(D21),Setup!$B$23*D21,0))/(IF(ISNUMBER(C21),Setup!$B$22,0)+IF(ISNUMBER(D21),Setup!$B$23,0))))</f>
+        <f>IF(B21="","",IF(AND(NOT(ISNUMBER(C21)),NOT(ISNUMBER(D21))),"",ROUND((IF(ISNUMBER(C21),Setup!$B$22*C21,0)+IF(ISNUMBER(D21),Setup!$B$23*D21,0))/(IF(ISNUMBER(C21),Setup!$B$22,0)+IF(ISNUMBER(D21),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G21" s="34">
@@ -14807,7 +14821,7 @@
         <v/>
       </c>
       <c r="F22" s="58">
-        <f>IF(B22="","",IF(AND(NOT(ISNUMBER(C22)),NOT(ISNUMBER(D22))),"",(IF(ISNUMBER(C22),Setup!$B$22*C22,0)+IF(ISNUMBER(D22),Setup!$B$23*D22,0))/(IF(ISNUMBER(C22),Setup!$B$22,0)+IF(ISNUMBER(D22),Setup!$B$23,0))))</f>
+        <f>IF(B22="","",IF(AND(NOT(ISNUMBER(C22)),NOT(ISNUMBER(D22))),"",ROUND((IF(ISNUMBER(C22),Setup!$B$22*C22,0)+IF(ISNUMBER(D22),Setup!$B$23*D22,0))/(IF(ISNUMBER(C22),Setup!$B$22,0)+IF(ISNUMBER(D22),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G22" s="34">
@@ -14876,7 +14890,7 @@
         <v/>
       </c>
       <c r="F23" s="58">
-        <f>IF(B23="","",IF(AND(NOT(ISNUMBER(C23)),NOT(ISNUMBER(D23))),"",(IF(ISNUMBER(C23),Setup!$B$22*C23,0)+IF(ISNUMBER(D23),Setup!$B$23*D23,0))/(IF(ISNUMBER(C23),Setup!$B$22,0)+IF(ISNUMBER(D23),Setup!$B$23,0))))</f>
+        <f>IF(B23="","",IF(AND(NOT(ISNUMBER(C23)),NOT(ISNUMBER(D23))),"",ROUND((IF(ISNUMBER(C23),Setup!$B$22*C23,0)+IF(ISNUMBER(D23),Setup!$B$23*D23,0))/(IF(ISNUMBER(C23),Setup!$B$22,0)+IF(ISNUMBER(D23),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G23" s="34">
@@ -14945,7 +14959,7 @@
         <v/>
       </c>
       <c r="F24" s="58">
-        <f>IF(B24="","",IF(AND(NOT(ISNUMBER(C24)),NOT(ISNUMBER(D24))),"",(IF(ISNUMBER(C24),Setup!$B$22*C24,0)+IF(ISNUMBER(D24),Setup!$B$23*D24,0))/(IF(ISNUMBER(C24),Setup!$B$22,0)+IF(ISNUMBER(D24),Setup!$B$23,0))))</f>
+        <f>IF(B24="","",IF(AND(NOT(ISNUMBER(C24)),NOT(ISNUMBER(D24))),"",ROUND((IF(ISNUMBER(C24),Setup!$B$22*C24,0)+IF(ISNUMBER(D24),Setup!$B$23*D24,0))/(IF(ISNUMBER(C24),Setup!$B$22,0)+IF(ISNUMBER(D24),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G24" s="34">
@@ -15014,7 +15028,7 @@
         <v/>
       </c>
       <c r="F25" s="58">
-        <f>IF(B25="","",IF(AND(NOT(ISNUMBER(C25)),NOT(ISNUMBER(D25))),"",(IF(ISNUMBER(C25),Setup!$B$22*C25,0)+IF(ISNUMBER(D25),Setup!$B$23*D25,0))/(IF(ISNUMBER(C25),Setup!$B$22,0)+IF(ISNUMBER(D25),Setup!$B$23,0))))</f>
+        <f>IF(B25="","",IF(AND(NOT(ISNUMBER(C25)),NOT(ISNUMBER(D25))),"",ROUND((IF(ISNUMBER(C25),Setup!$B$22*C25,0)+IF(ISNUMBER(D25),Setup!$B$23*D25,0))/(IF(ISNUMBER(C25),Setup!$B$22,0)+IF(ISNUMBER(D25),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G25" s="34">
@@ -15083,7 +15097,7 @@
         <v/>
       </c>
       <c r="F26" s="58">
-        <f>IF(B26="","",IF(AND(NOT(ISNUMBER(C26)),NOT(ISNUMBER(D26))),"",(IF(ISNUMBER(C26),Setup!$B$22*C26,0)+IF(ISNUMBER(D26),Setup!$B$23*D26,0))/(IF(ISNUMBER(C26),Setup!$B$22,0)+IF(ISNUMBER(D26),Setup!$B$23,0))))</f>
+        <f>IF(B26="","",IF(AND(NOT(ISNUMBER(C26)),NOT(ISNUMBER(D26))),"",ROUND((IF(ISNUMBER(C26),Setup!$B$22*C26,0)+IF(ISNUMBER(D26),Setup!$B$23*D26,0))/(IF(ISNUMBER(C26),Setup!$B$22,0)+IF(ISNUMBER(D26),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G26" s="34">
@@ -15152,7 +15166,7 @@
         <v/>
       </c>
       <c r="F27" s="58">
-        <f>IF(B27="","",IF(AND(NOT(ISNUMBER(C27)),NOT(ISNUMBER(D27))),"",(IF(ISNUMBER(C27),Setup!$B$22*C27,0)+IF(ISNUMBER(D27),Setup!$B$23*D27,0))/(IF(ISNUMBER(C27),Setup!$B$22,0)+IF(ISNUMBER(D27),Setup!$B$23,0))))</f>
+        <f>IF(B27="","",IF(AND(NOT(ISNUMBER(C27)),NOT(ISNUMBER(D27))),"",ROUND((IF(ISNUMBER(C27),Setup!$B$22*C27,0)+IF(ISNUMBER(D27),Setup!$B$23*D27,0))/(IF(ISNUMBER(C27),Setup!$B$22,0)+IF(ISNUMBER(D27),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G27" s="34">
@@ -15221,7 +15235,7 @@
         <v/>
       </c>
       <c r="F28" s="58">
-        <f>IF(B28="","",IF(AND(NOT(ISNUMBER(C28)),NOT(ISNUMBER(D28))),"",(IF(ISNUMBER(C28),Setup!$B$22*C28,0)+IF(ISNUMBER(D28),Setup!$B$23*D28,0))/(IF(ISNUMBER(C28),Setup!$B$22,0)+IF(ISNUMBER(D28),Setup!$B$23,0))))</f>
+        <f>IF(B28="","",IF(AND(NOT(ISNUMBER(C28)),NOT(ISNUMBER(D28))),"",ROUND((IF(ISNUMBER(C28),Setup!$B$22*C28,0)+IF(ISNUMBER(D28),Setup!$B$23*D28,0))/(IF(ISNUMBER(C28),Setup!$B$22,0)+IF(ISNUMBER(D28),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G28" s="34">
@@ -15290,7 +15304,7 @@
         <v/>
       </c>
       <c r="F29" s="58">
-        <f>IF(B29="","",IF(AND(NOT(ISNUMBER(C29)),NOT(ISNUMBER(D29))),"",(IF(ISNUMBER(C29),Setup!$B$22*C29,0)+IF(ISNUMBER(D29),Setup!$B$23*D29,0))/(IF(ISNUMBER(C29),Setup!$B$22,0)+IF(ISNUMBER(D29),Setup!$B$23,0))))</f>
+        <f>IF(B29="","",IF(AND(NOT(ISNUMBER(C29)),NOT(ISNUMBER(D29))),"",ROUND((IF(ISNUMBER(C29),Setup!$B$22*C29,0)+IF(ISNUMBER(D29),Setup!$B$23*D29,0))/(IF(ISNUMBER(C29),Setup!$B$22,0)+IF(ISNUMBER(D29),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G29" s="34">
@@ -15359,7 +15373,7 @@
         <v/>
       </c>
       <c r="F30" s="58">
-        <f>IF(B30="","",IF(AND(NOT(ISNUMBER(C30)),NOT(ISNUMBER(D30))),"",(IF(ISNUMBER(C30),Setup!$B$22*C30,0)+IF(ISNUMBER(D30),Setup!$B$23*D30,0))/(IF(ISNUMBER(C30),Setup!$B$22,0)+IF(ISNUMBER(D30),Setup!$B$23,0))))</f>
+        <f>IF(B30="","",IF(AND(NOT(ISNUMBER(C30)),NOT(ISNUMBER(D30))),"",ROUND((IF(ISNUMBER(C30),Setup!$B$22*C30,0)+IF(ISNUMBER(D30),Setup!$B$23*D30,0))/(IF(ISNUMBER(C30),Setup!$B$22,0)+IF(ISNUMBER(D30),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G30" s="34">
@@ -15428,7 +15442,7 @@
         <v/>
       </c>
       <c r="F31" s="58">
-        <f>IF(B31="","",IF(AND(NOT(ISNUMBER(C31)),NOT(ISNUMBER(D31))),"",(IF(ISNUMBER(C31),Setup!$B$22*C31,0)+IF(ISNUMBER(D31),Setup!$B$23*D31,0))/(IF(ISNUMBER(C31),Setup!$B$22,0)+IF(ISNUMBER(D31),Setup!$B$23,0))))</f>
+        <f>IF(B31="","",IF(AND(NOT(ISNUMBER(C31)),NOT(ISNUMBER(D31))),"",ROUND((IF(ISNUMBER(C31),Setup!$B$22*C31,0)+IF(ISNUMBER(D31),Setup!$B$23*D31,0))/(IF(ISNUMBER(C31),Setup!$B$22,0)+IF(ISNUMBER(D31),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G31" s="34">
@@ -15497,7 +15511,7 @@
         <v/>
       </c>
       <c r="F32" s="58">
-        <f>IF(B32="","",IF(AND(NOT(ISNUMBER(C32)),NOT(ISNUMBER(D32))),"",(IF(ISNUMBER(C32),Setup!$B$22*C32,0)+IF(ISNUMBER(D32),Setup!$B$23*D32,0))/(IF(ISNUMBER(C32),Setup!$B$22,0)+IF(ISNUMBER(D32),Setup!$B$23,0))))</f>
+        <f>IF(B32="","",IF(AND(NOT(ISNUMBER(C32)),NOT(ISNUMBER(D32))),"",ROUND((IF(ISNUMBER(C32),Setup!$B$22*C32,0)+IF(ISNUMBER(D32),Setup!$B$23*D32,0))/(IF(ISNUMBER(C32),Setup!$B$22,0)+IF(ISNUMBER(D32),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G32" s="34">
@@ -15566,7 +15580,7 @@
         <v/>
       </c>
       <c r="F33" s="58">
-        <f>IF(B33="","",IF(AND(NOT(ISNUMBER(C33)),NOT(ISNUMBER(D33))),"",(IF(ISNUMBER(C33),Setup!$B$22*C33,0)+IF(ISNUMBER(D33),Setup!$B$23*D33,0))/(IF(ISNUMBER(C33),Setup!$B$22,0)+IF(ISNUMBER(D33),Setup!$B$23,0))))</f>
+        <f>IF(B33="","",IF(AND(NOT(ISNUMBER(C33)),NOT(ISNUMBER(D33))),"",ROUND((IF(ISNUMBER(C33),Setup!$B$22*C33,0)+IF(ISNUMBER(D33),Setup!$B$23*D33,0))/(IF(ISNUMBER(C33),Setup!$B$22,0)+IF(ISNUMBER(D33),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G33" s="34">
@@ -15635,7 +15649,7 @@
         <v/>
       </c>
       <c r="F34" s="58">
-        <f>IF(B34="","",IF(AND(NOT(ISNUMBER(C34)),NOT(ISNUMBER(D34))),"",(IF(ISNUMBER(C34),Setup!$B$22*C34,0)+IF(ISNUMBER(D34),Setup!$B$23*D34,0))/(IF(ISNUMBER(C34),Setup!$B$22,0)+IF(ISNUMBER(D34),Setup!$B$23,0))))</f>
+        <f>IF(B34="","",IF(AND(NOT(ISNUMBER(C34)),NOT(ISNUMBER(D34))),"",ROUND((IF(ISNUMBER(C34),Setup!$B$22*C34,0)+IF(ISNUMBER(D34),Setup!$B$23*D34,0))/(IF(ISNUMBER(C34),Setup!$B$22,0)+IF(ISNUMBER(D34),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G34" s="34">
@@ -15704,7 +15718,7 @@
         <v/>
       </c>
       <c r="F35" s="58">
-        <f>IF(B35="","",IF(AND(NOT(ISNUMBER(C35)),NOT(ISNUMBER(D35))),"",(IF(ISNUMBER(C35),Setup!$B$22*C35,0)+IF(ISNUMBER(D35),Setup!$B$23*D35,0))/(IF(ISNUMBER(C35),Setup!$B$22,0)+IF(ISNUMBER(D35),Setup!$B$23,0))))</f>
+        <f>IF(B35="","",IF(AND(NOT(ISNUMBER(C35)),NOT(ISNUMBER(D35))),"",ROUND((IF(ISNUMBER(C35),Setup!$B$22*C35,0)+IF(ISNUMBER(D35),Setup!$B$23*D35,0))/(IF(ISNUMBER(C35),Setup!$B$22,0)+IF(ISNUMBER(D35),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G35" s="34">
@@ -15773,7 +15787,7 @@
         <v/>
       </c>
       <c r="F36" s="58">
-        <f>IF(B36="","",IF(AND(NOT(ISNUMBER(C36)),NOT(ISNUMBER(D36))),"",(IF(ISNUMBER(C36),Setup!$B$22*C36,0)+IF(ISNUMBER(D36),Setup!$B$23*D36,0))/(IF(ISNUMBER(C36),Setup!$B$22,0)+IF(ISNUMBER(D36),Setup!$B$23,0))))</f>
+        <f>IF(B36="","",IF(AND(NOT(ISNUMBER(C36)),NOT(ISNUMBER(D36))),"",ROUND((IF(ISNUMBER(C36),Setup!$B$22*C36,0)+IF(ISNUMBER(D36),Setup!$B$23*D36,0))/(IF(ISNUMBER(C36),Setup!$B$22,0)+IF(ISNUMBER(D36),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G36" s="34">
@@ -15842,7 +15856,7 @@
         <v/>
       </c>
       <c r="F37" s="58">
-        <f>IF(B37="","",IF(AND(NOT(ISNUMBER(C37)),NOT(ISNUMBER(D37))),"",(IF(ISNUMBER(C37),Setup!$B$22*C37,0)+IF(ISNUMBER(D37),Setup!$B$23*D37,0))/(IF(ISNUMBER(C37),Setup!$B$22,0)+IF(ISNUMBER(D37),Setup!$B$23,0))))</f>
+        <f>IF(B37="","",IF(AND(NOT(ISNUMBER(C37)),NOT(ISNUMBER(D37))),"",ROUND((IF(ISNUMBER(C37),Setup!$B$22*C37,0)+IF(ISNUMBER(D37),Setup!$B$23*D37,0))/(IF(ISNUMBER(C37),Setup!$B$22,0)+IF(ISNUMBER(D37),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G37" s="34">
@@ -15911,7 +15925,7 @@
         <v/>
       </c>
       <c r="F38" s="58">
-        <f>IF(B38="","",IF(AND(NOT(ISNUMBER(C38)),NOT(ISNUMBER(D38))),"",(IF(ISNUMBER(C38),Setup!$B$22*C38,0)+IF(ISNUMBER(D38),Setup!$B$23*D38,0))/(IF(ISNUMBER(C38),Setup!$B$22,0)+IF(ISNUMBER(D38),Setup!$B$23,0))))</f>
+        <f>IF(B38="","",IF(AND(NOT(ISNUMBER(C38)),NOT(ISNUMBER(D38))),"",ROUND((IF(ISNUMBER(C38),Setup!$B$22*C38,0)+IF(ISNUMBER(D38),Setup!$B$23*D38,0))/(IF(ISNUMBER(C38),Setup!$B$22,0)+IF(ISNUMBER(D38),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G38" s="34">
@@ -15980,7 +15994,7 @@
         <v/>
       </c>
       <c r="F39" s="58">
-        <f>IF(B39="","",IF(AND(NOT(ISNUMBER(C39)),NOT(ISNUMBER(D39))),"",(IF(ISNUMBER(C39),Setup!$B$22*C39,0)+IF(ISNUMBER(D39),Setup!$B$23*D39,0))/(IF(ISNUMBER(C39),Setup!$B$22,0)+IF(ISNUMBER(D39),Setup!$B$23,0))))</f>
+        <f>IF(B39="","",IF(AND(NOT(ISNUMBER(C39)),NOT(ISNUMBER(D39))),"",ROUND((IF(ISNUMBER(C39),Setup!$B$22*C39,0)+IF(ISNUMBER(D39),Setup!$B$23*D39,0))/(IF(ISNUMBER(C39),Setup!$B$22,0)+IF(ISNUMBER(D39),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G39" s="34">
@@ -16049,7 +16063,7 @@
         <v/>
       </c>
       <c r="F40" s="58">
-        <f>IF(B40="","",IF(AND(NOT(ISNUMBER(C40)),NOT(ISNUMBER(D40))),"",(IF(ISNUMBER(C40),Setup!$B$22*C40,0)+IF(ISNUMBER(D40),Setup!$B$23*D40,0))/(IF(ISNUMBER(C40),Setup!$B$22,0)+IF(ISNUMBER(D40),Setup!$B$23,0))))</f>
+        <f>IF(B40="","",IF(AND(NOT(ISNUMBER(C40)),NOT(ISNUMBER(D40))),"",ROUND((IF(ISNUMBER(C40),Setup!$B$22*C40,0)+IF(ISNUMBER(D40),Setup!$B$23*D40,0))/(IF(ISNUMBER(C40),Setup!$B$22,0)+IF(ISNUMBER(D40),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G40" s="34">
@@ -16118,7 +16132,7 @@
         <v/>
       </c>
       <c r="F41" s="58">
-        <f>IF(B41="","",IF(AND(NOT(ISNUMBER(C41)),NOT(ISNUMBER(D41))),"",(IF(ISNUMBER(C41),Setup!$B$22*C41,0)+IF(ISNUMBER(D41),Setup!$B$23*D41,0))/(IF(ISNUMBER(C41),Setup!$B$22,0)+IF(ISNUMBER(D41),Setup!$B$23,0))))</f>
+        <f>IF(B41="","",IF(AND(NOT(ISNUMBER(C41)),NOT(ISNUMBER(D41))),"",ROUND((IF(ISNUMBER(C41),Setup!$B$22*C41,0)+IF(ISNUMBER(D41),Setup!$B$23*D41,0))/(IF(ISNUMBER(C41),Setup!$B$22,0)+IF(ISNUMBER(D41),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G41" s="34">
@@ -16187,7 +16201,7 @@
         <v/>
       </c>
       <c r="F42" s="58">
-        <f>IF(B42="","",IF(AND(NOT(ISNUMBER(C42)),NOT(ISNUMBER(D42))),"",(IF(ISNUMBER(C42),Setup!$B$22*C42,0)+IF(ISNUMBER(D42),Setup!$B$23*D42,0))/(IF(ISNUMBER(C42),Setup!$B$22,0)+IF(ISNUMBER(D42),Setup!$B$23,0))))</f>
+        <f>IF(B42="","",IF(AND(NOT(ISNUMBER(C42)),NOT(ISNUMBER(D42))),"",ROUND((IF(ISNUMBER(C42),Setup!$B$22*C42,0)+IF(ISNUMBER(D42),Setup!$B$23*D42,0))/(IF(ISNUMBER(C42),Setup!$B$22,0)+IF(ISNUMBER(D42),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G42" s="34">
@@ -16256,7 +16270,7 @@
         <v/>
       </c>
       <c r="F43" s="58">
-        <f>IF(B43="","",IF(AND(NOT(ISNUMBER(C43)),NOT(ISNUMBER(D43))),"",(IF(ISNUMBER(C43),Setup!$B$22*C43,0)+IF(ISNUMBER(D43),Setup!$B$23*D43,0))/(IF(ISNUMBER(C43),Setup!$B$22,0)+IF(ISNUMBER(D43),Setup!$B$23,0))))</f>
+        <f>IF(B43="","",IF(AND(NOT(ISNUMBER(C43)),NOT(ISNUMBER(D43))),"",ROUND((IF(ISNUMBER(C43),Setup!$B$22*C43,0)+IF(ISNUMBER(D43),Setup!$B$23*D43,0))/(IF(ISNUMBER(C43),Setup!$B$22,0)+IF(ISNUMBER(D43),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G43" s="34">
@@ -16325,7 +16339,7 @@
         <v/>
       </c>
       <c r="F44" s="58">
-        <f>IF(B44="","",IF(AND(NOT(ISNUMBER(C44)),NOT(ISNUMBER(D44))),"",(IF(ISNUMBER(C44),Setup!$B$22*C44,0)+IF(ISNUMBER(D44),Setup!$B$23*D44,0))/(IF(ISNUMBER(C44),Setup!$B$22,0)+IF(ISNUMBER(D44),Setup!$B$23,0))))</f>
+        <f>IF(B44="","",IF(AND(NOT(ISNUMBER(C44)),NOT(ISNUMBER(D44))),"",ROUND((IF(ISNUMBER(C44),Setup!$B$22*C44,0)+IF(ISNUMBER(D44),Setup!$B$23*D44,0))/(IF(ISNUMBER(C44),Setup!$B$22,0)+IF(ISNUMBER(D44),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G44" s="34">
@@ -16394,7 +16408,7 @@
         <v/>
       </c>
       <c r="F45" s="58">
-        <f>IF(B45="","",IF(AND(NOT(ISNUMBER(C45)),NOT(ISNUMBER(D45))),"",(IF(ISNUMBER(C45),Setup!$B$22*C45,0)+IF(ISNUMBER(D45),Setup!$B$23*D45,0))/(IF(ISNUMBER(C45),Setup!$B$22,0)+IF(ISNUMBER(D45),Setup!$B$23,0))))</f>
+        <f>IF(B45="","",IF(AND(NOT(ISNUMBER(C45)),NOT(ISNUMBER(D45))),"",ROUND((IF(ISNUMBER(C45),Setup!$B$22*C45,0)+IF(ISNUMBER(D45),Setup!$B$23*D45,0))/(IF(ISNUMBER(C45),Setup!$B$22,0)+IF(ISNUMBER(D45),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G45" s="34">
@@ -16463,7 +16477,7 @@
         <v/>
       </c>
       <c r="F46" s="58">
-        <f>IF(B46="","",IF(AND(NOT(ISNUMBER(C46)),NOT(ISNUMBER(D46))),"",(IF(ISNUMBER(C46),Setup!$B$22*C46,0)+IF(ISNUMBER(D46),Setup!$B$23*D46,0))/(IF(ISNUMBER(C46),Setup!$B$22,0)+IF(ISNUMBER(D46),Setup!$B$23,0))))</f>
+        <f>IF(B46="","",IF(AND(NOT(ISNUMBER(C46)),NOT(ISNUMBER(D46))),"",ROUND((IF(ISNUMBER(C46),Setup!$B$22*C46,0)+IF(ISNUMBER(D46),Setup!$B$23*D46,0))/(IF(ISNUMBER(C46),Setup!$B$22,0)+IF(ISNUMBER(D46),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G46" s="34">
@@ -16532,7 +16546,7 @@
         <v/>
       </c>
       <c r="F47" s="58">
-        <f>IF(B47="","",IF(AND(NOT(ISNUMBER(C47)),NOT(ISNUMBER(D47))),"",(IF(ISNUMBER(C47),Setup!$B$22*C47,0)+IF(ISNUMBER(D47),Setup!$B$23*D47,0))/(IF(ISNUMBER(C47),Setup!$B$22,0)+IF(ISNUMBER(D47),Setup!$B$23,0))))</f>
+        <f>IF(B47="","",IF(AND(NOT(ISNUMBER(C47)),NOT(ISNUMBER(D47))),"",ROUND((IF(ISNUMBER(C47),Setup!$B$22*C47,0)+IF(ISNUMBER(D47),Setup!$B$23*D47,0))/(IF(ISNUMBER(C47),Setup!$B$22,0)+IF(ISNUMBER(D47),Setup!$B$23,0)),9)))</f>
         <v/>
       </c>
       <c r="G47" s="34">
@@ -16582,10 +16596,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K8:K47">
-    <cfRule type="expression" priority="1" dxfId="7">
+    <cfRule type="expression" priority="1" dxfId="8">
       <formula>K8="At risk"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="8">
+    <cfRule type="expression" priority="2" dxfId="9">
       <formula>K8="Watch"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16877,7 +16891,7 @@
         <v/>
       </c>
       <c r="H15" s="70">
-        <f>IF(OR(A15="",$H$4=""),"",IF(ISNUMBER(F15),"Turned in",IF(UPPER(F15)="EX","Excused",IF(OR(UPPER(F15)="M",Assignments!I6=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A15="",$H$4=""),"",IF(ISNUMBER(F15),"Submitted",IF(UPPER(F15)="EX","Excused",IF(OR(UPPER(F15)="M",Assignments!I6=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -16911,7 +16925,7 @@
         <v/>
       </c>
       <c r="H16" s="70">
-        <f>IF(OR(A16="",$H$4=""),"",IF(ISNUMBER(F16),"Turned in",IF(UPPER(F16)="EX","Excused",IF(OR(UPPER(F16)="M",Assignments!I7=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A16="",$H$4=""),"",IF(ISNUMBER(F16),"Submitted",IF(UPPER(F16)="EX","Excused",IF(OR(UPPER(F16)="M",Assignments!I7=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -16945,7 +16959,7 @@
         <v/>
       </c>
       <c r="H17" s="70">
-        <f>IF(OR(A17="",$H$4=""),"",IF(ISNUMBER(F17),"Turned in",IF(UPPER(F17)="EX","Excused",IF(OR(UPPER(F17)="M",Assignments!I8=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A17="",$H$4=""),"",IF(ISNUMBER(F17),"Submitted",IF(UPPER(F17)="EX","Excused",IF(OR(UPPER(F17)="M",Assignments!I8=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -16979,7 +16993,7 @@
         <v/>
       </c>
       <c r="H18" s="70">
-        <f>IF(OR(A18="",$H$4=""),"",IF(ISNUMBER(F18),"Turned in",IF(UPPER(F18)="EX","Excused",IF(OR(UPPER(F18)="M",Assignments!I9=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A18="",$H$4=""),"",IF(ISNUMBER(F18),"Submitted",IF(UPPER(F18)="EX","Excused",IF(OR(UPPER(F18)="M",Assignments!I9=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17013,7 +17027,7 @@
         <v/>
       </c>
       <c r="H19" s="70">
-        <f>IF(OR(A19="",$H$4=""),"",IF(ISNUMBER(F19),"Turned in",IF(UPPER(F19)="EX","Excused",IF(OR(UPPER(F19)="M",Assignments!I10=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A19="",$H$4=""),"",IF(ISNUMBER(F19),"Submitted",IF(UPPER(F19)="EX","Excused",IF(OR(UPPER(F19)="M",Assignments!I10=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17047,7 +17061,7 @@
         <v/>
       </c>
       <c r="H20" s="70">
-        <f>IF(OR(A20="",$H$4=""),"",IF(ISNUMBER(F20),"Turned in",IF(UPPER(F20)="EX","Excused",IF(OR(UPPER(F20)="M",Assignments!I11=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A20="",$H$4=""),"",IF(ISNUMBER(F20),"Submitted",IF(UPPER(F20)="EX","Excused",IF(OR(UPPER(F20)="M",Assignments!I11=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17081,7 +17095,7 @@
         <v/>
       </c>
       <c r="H21" s="70">
-        <f>IF(OR(A21="",$H$4=""),"",IF(ISNUMBER(F21),"Turned in",IF(UPPER(F21)="EX","Excused",IF(OR(UPPER(F21)="M",Assignments!I12=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A21="",$H$4=""),"",IF(ISNUMBER(F21),"Submitted",IF(UPPER(F21)="EX","Excused",IF(OR(UPPER(F21)="M",Assignments!I12=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17115,7 +17129,7 @@
         <v/>
       </c>
       <c r="H22" s="70">
-        <f>IF(OR(A22="",$H$4=""),"",IF(ISNUMBER(F22),"Turned in",IF(UPPER(F22)="EX","Excused",IF(OR(UPPER(F22)="M",Assignments!I13=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A22="",$H$4=""),"",IF(ISNUMBER(F22),"Submitted",IF(UPPER(F22)="EX","Excused",IF(OR(UPPER(F22)="M",Assignments!I13=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17149,7 +17163,7 @@
         <v/>
       </c>
       <c r="H23" s="70">
-        <f>IF(OR(A23="",$H$4=""),"",IF(ISNUMBER(F23),"Turned in",IF(UPPER(F23)="EX","Excused",IF(OR(UPPER(F23)="M",Assignments!I14=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A23="",$H$4=""),"",IF(ISNUMBER(F23),"Submitted",IF(UPPER(F23)="EX","Excused",IF(OR(UPPER(F23)="M",Assignments!I14=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17183,7 +17197,7 @@
         <v/>
       </c>
       <c r="H24" s="70">
-        <f>IF(OR(A24="",$H$4=""),"",IF(ISNUMBER(F24),"Turned in",IF(UPPER(F24)="EX","Excused",IF(OR(UPPER(F24)="M",Assignments!I15=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A24="",$H$4=""),"",IF(ISNUMBER(F24),"Submitted",IF(UPPER(F24)="EX","Excused",IF(OR(UPPER(F24)="M",Assignments!I15=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17217,7 +17231,7 @@
         <v/>
       </c>
       <c r="H25" s="70">
-        <f>IF(OR(A25="",$H$4=""),"",IF(ISNUMBER(F25),"Turned in",IF(UPPER(F25)="EX","Excused",IF(OR(UPPER(F25)="M",Assignments!I16=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A25="",$H$4=""),"",IF(ISNUMBER(F25),"Submitted",IF(UPPER(F25)="EX","Excused",IF(OR(UPPER(F25)="M",Assignments!I16=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17251,7 +17265,7 @@
         <v/>
       </c>
       <c r="H26" s="70">
-        <f>IF(OR(A26="",$H$4=""),"",IF(ISNUMBER(F26),"Turned in",IF(UPPER(F26)="EX","Excused",IF(OR(UPPER(F26)="M",Assignments!I17=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A26="",$H$4=""),"",IF(ISNUMBER(F26),"Submitted",IF(UPPER(F26)="EX","Excused",IF(OR(UPPER(F26)="M",Assignments!I17=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17285,7 +17299,7 @@
         <v/>
       </c>
       <c r="H27" s="70">
-        <f>IF(OR(A27="",$H$4=""),"",IF(ISNUMBER(F27),"Turned in",IF(UPPER(F27)="EX","Excused",IF(OR(UPPER(F27)="M",Assignments!I18=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A27="",$H$4=""),"",IF(ISNUMBER(F27),"Submitted",IF(UPPER(F27)="EX","Excused",IF(OR(UPPER(F27)="M",Assignments!I18=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17319,7 +17333,7 @@
         <v/>
       </c>
       <c r="H28" s="70">
-        <f>IF(OR(A28="",$H$4=""),"",IF(ISNUMBER(F28),"Turned in",IF(UPPER(F28)="EX","Excused",IF(OR(UPPER(F28)="M",Assignments!I19=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A28="",$H$4=""),"",IF(ISNUMBER(F28),"Submitted",IF(UPPER(F28)="EX","Excused",IF(OR(UPPER(F28)="M",Assignments!I19=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17353,7 +17367,7 @@
         <v/>
       </c>
       <c r="H29" s="70">
-        <f>IF(OR(A29="",$H$4=""),"",IF(ISNUMBER(F29),"Turned in",IF(UPPER(F29)="EX","Excused",IF(OR(UPPER(F29)="M",Assignments!I20=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A29="",$H$4=""),"",IF(ISNUMBER(F29),"Submitted",IF(UPPER(F29)="EX","Excused",IF(OR(UPPER(F29)="M",Assignments!I20=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17387,7 +17401,7 @@
         <v/>
       </c>
       <c r="H30" s="70">
-        <f>IF(OR(A30="",$H$4=""),"",IF(ISNUMBER(F30),"Turned in",IF(UPPER(F30)="EX","Excused",IF(OR(UPPER(F30)="M",Assignments!I21=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A30="",$H$4=""),"",IF(ISNUMBER(F30),"Submitted",IF(UPPER(F30)="EX","Excused",IF(OR(UPPER(F30)="M",Assignments!I21=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17421,7 +17435,7 @@
         <v/>
       </c>
       <c r="H31" s="70">
-        <f>IF(OR(A31="",$H$4=""),"",IF(ISNUMBER(F31),"Turned in",IF(UPPER(F31)="EX","Excused",IF(OR(UPPER(F31)="M",Assignments!I22=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A31="",$H$4=""),"",IF(ISNUMBER(F31),"Submitted",IF(UPPER(F31)="EX","Excused",IF(OR(UPPER(F31)="M",Assignments!I22=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17455,7 +17469,7 @@
         <v/>
       </c>
       <c r="H32" s="70">
-        <f>IF(OR(A32="",$H$4=""),"",IF(ISNUMBER(F32),"Turned in",IF(UPPER(F32)="EX","Excused",IF(OR(UPPER(F32)="M",Assignments!I23=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A32="",$H$4=""),"",IF(ISNUMBER(F32),"Submitted",IF(UPPER(F32)="EX","Excused",IF(OR(UPPER(F32)="M",Assignments!I23=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17489,7 +17503,7 @@
         <v/>
       </c>
       <c r="H33" s="70">
-        <f>IF(OR(A33="",$H$4=""),"",IF(ISNUMBER(F33),"Turned in",IF(UPPER(F33)="EX","Excused",IF(OR(UPPER(F33)="M",Assignments!I24=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A33="",$H$4=""),"",IF(ISNUMBER(F33),"Submitted",IF(UPPER(F33)="EX","Excused",IF(OR(UPPER(F33)="M",Assignments!I24=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17523,7 +17537,7 @@
         <v/>
       </c>
       <c r="H34" s="70">
-        <f>IF(OR(A34="",$H$4=""),"",IF(ISNUMBER(F34),"Turned in",IF(UPPER(F34)="EX","Excused",IF(OR(UPPER(F34)="M",Assignments!I25=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A34="",$H$4=""),"",IF(ISNUMBER(F34),"Submitted",IF(UPPER(F34)="EX","Excused",IF(OR(UPPER(F34)="M",Assignments!I25=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17557,7 +17571,7 @@
         <v/>
       </c>
       <c r="H35" s="70">
-        <f>IF(OR(A35="",$H$4=""),"",IF(ISNUMBER(F35),"Turned in",IF(UPPER(F35)="EX","Excused",IF(OR(UPPER(F35)="M",Assignments!I26=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A35="",$H$4=""),"",IF(ISNUMBER(F35),"Submitted",IF(UPPER(F35)="EX","Excused",IF(OR(UPPER(F35)="M",Assignments!I26=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17591,7 +17605,7 @@
         <v/>
       </c>
       <c r="H36" s="70">
-        <f>IF(OR(A36="",$H$4=""),"",IF(ISNUMBER(F36),"Turned in",IF(UPPER(F36)="EX","Excused",IF(OR(UPPER(F36)="M",Assignments!I27=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A36="",$H$4=""),"",IF(ISNUMBER(F36),"Submitted",IF(UPPER(F36)="EX","Excused",IF(OR(UPPER(F36)="M",Assignments!I27=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17625,7 +17639,7 @@
         <v/>
       </c>
       <c r="H37" s="70">
-        <f>IF(OR(A37="",$H$4=""),"",IF(ISNUMBER(F37),"Turned in",IF(UPPER(F37)="EX","Excused",IF(OR(UPPER(F37)="M",Assignments!I28=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A37="",$H$4=""),"",IF(ISNUMBER(F37),"Submitted",IF(UPPER(F37)="EX","Excused",IF(OR(UPPER(F37)="M",Assignments!I28=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17659,7 +17673,7 @@
         <v/>
       </c>
       <c r="H38" s="70">
-        <f>IF(OR(A38="",$H$4=""),"",IF(ISNUMBER(F38),"Turned in",IF(UPPER(F38)="EX","Excused",IF(OR(UPPER(F38)="M",Assignments!I29=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A38="",$H$4=""),"",IF(ISNUMBER(F38),"Submitted",IF(UPPER(F38)="EX","Excused",IF(OR(UPPER(F38)="M",Assignments!I29=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17693,7 +17707,7 @@
         <v/>
       </c>
       <c r="H39" s="70">
-        <f>IF(OR(A39="",$H$4=""),"",IF(ISNUMBER(F39),"Turned in",IF(UPPER(F39)="EX","Excused",IF(OR(UPPER(F39)="M",Assignments!I30=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A39="",$H$4=""),"",IF(ISNUMBER(F39),"Submitted",IF(UPPER(F39)="EX","Excused",IF(OR(UPPER(F39)="M",Assignments!I30=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17727,7 +17741,7 @@
         <v/>
       </c>
       <c r="H40" s="70">
-        <f>IF(OR(A40="",$H$4=""),"",IF(ISNUMBER(F40),"Turned in",IF(UPPER(F40)="EX","Excused",IF(OR(UPPER(F40)="M",Assignments!I31=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A40="",$H$4=""),"",IF(ISNUMBER(F40),"Submitted",IF(UPPER(F40)="EX","Excused",IF(OR(UPPER(F40)="M",Assignments!I31=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17761,7 +17775,7 @@
         <v/>
       </c>
       <c r="H41" s="70">
-        <f>IF(OR(A41="",$H$4=""),"",IF(ISNUMBER(F41),"Turned in",IF(UPPER(F41)="EX","Excused",IF(OR(UPPER(F41)="M",Assignments!I32=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A41="",$H$4=""),"",IF(ISNUMBER(F41),"Submitted",IF(UPPER(F41)="EX","Excused",IF(OR(UPPER(F41)="M",Assignments!I32=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17795,7 +17809,7 @@
         <v/>
       </c>
       <c r="H42" s="70">
-        <f>IF(OR(A42="",$H$4=""),"",IF(ISNUMBER(F42),"Turned in",IF(UPPER(F42)="EX","Excused",IF(OR(UPPER(F42)="M",Assignments!I33=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A42="",$H$4=""),"",IF(ISNUMBER(F42),"Submitted",IF(UPPER(F42)="EX","Excused",IF(OR(UPPER(F42)="M",Assignments!I33=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17829,7 +17843,7 @@
         <v/>
       </c>
       <c r="H43" s="70">
-        <f>IF(OR(A43="",$H$4=""),"",IF(ISNUMBER(F43),"Turned in",IF(UPPER(F43)="EX","Excused",IF(OR(UPPER(F43)="M",Assignments!I34=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A43="",$H$4=""),"",IF(ISNUMBER(F43),"Submitted",IF(UPPER(F43)="EX","Excused",IF(OR(UPPER(F43)="M",Assignments!I34=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17863,7 +17877,7 @@
         <v/>
       </c>
       <c r="H44" s="70">
-        <f>IF(OR(A44="",$H$4=""),"",IF(ISNUMBER(F44),"Turned in",IF(UPPER(F44)="EX","Excused",IF(OR(UPPER(F44)="M",Assignments!I35=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A44="",$H$4=""),"",IF(ISNUMBER(F44),"Submitted",IF(UPPER(F44)="EX","Excused",IF(OR(UPPER(F44)="M",Assignments!I35=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17897,7 +17911,7 @@
         <v/>
       </c>
       <c r="H45" s="70">
-        <f>IF(OR(A45="",$H$4=""),"",IF(ISNUMBER(F45),"Turned in",IF(UPPER(F45)="EX","Excused",IF(OR(UPPER(F45)="M",Assignments!I36=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A45="",$H$4=""),"",IF(ISNUMBER(F45),"Submitted",IF(UPPER(F45)="EX","Excused",IF(OR(UPPER(F45)="M",Assignments!I36=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17931,7 +17945,7 @@
         <v/>
       </c>
       <c r="H46" s="70">
-        <f>IF(OR(A46="",$H$4=""),"",IF(ISNUMBER(F46),"Turned in",IF(UPPER(F46)="EX","Excused",IF(OR(UPPER(F46)="M",Assignments!I37=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A46="",$H$4=""),"",IF(ISNUMBER(F46),"Submitted",IF(UPPER(F46)="EX","Excused",IF(OR(UPPER(F46)="M",Assignments!I37=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17965,7 +17979,7 @@
         <v/>
       </c>
       <c r="H47" s="70">
-        <f>IF(OR(A47="",$H$4=""),"",IF(ISNUMBER(F47),"Turned in",IF(UPPER(F47)="EX","Excused",IF(OR(UPPER(F47)="M",Assignments!I38=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A47="",$H$4=""),"",IF(ISNUMBER(F47),"Submitted",IF(UPPER(F47)="EX","Excused",IF(OR(UPPER(F47)="M",Assignments!I38=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -17999,7 +18013,7 @@
         <v/>
       </c>
       <c r="H48" s="70">
-        <f>IF(OR(A48="",$H$4=""),"",IF(ISNUMBER(F48),"Turned in",IF(UPPER(F48)="EX","Excused",IF(OR(UPPER(F48)="M",Assignments!I39=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A48="",$H$4=""),"",IF(ISNUMBER(F48),"Submitted",IF(UPPER(F48)="EX","Excused",IF(OR(UPPER(F48)="M",Assignments!I39=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18033,7 +18047,7 @@
         <v/>
       </c>
       <c r="H49" s="70">
-        <f>IF(OR(A49="",$H$4=""),"",IF(ISNUMBER(F49),"Turned in",IF(UPPER(F49)="EX","Excused",IF(OR(UPPER(F49)="M",Assignments!I40=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A49="",$H$4=""),"",IF(ISNUMBER(F49),"Submitted",IF(UPPER(F49)="EX","Excused",IF(OR(UPPER(F49)="M",Assignments!I40=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18067,7 +18081,7 @@
         <v/>
       </c>
       <c r="H50" s="70">
-        <f>IF(OR(A50="",$H$4=""),"",IF(ISNUMBER(F50),"Turned in",IF(UPPER(F50)="EX","Excused",IF(OR(UPPER(F50)="M",Assignments!I41=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A50="",$H$4=""),"",IF(ISNUMBER(F50),"Submitted",IF(UPPER(F50)="EX","Excused",IF(OR(UPPER(F50)="M",Assignments!I41=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18101,7 +18115,7 @@
         <v/>
       </c>
       <c r="H51" s="70">
-        <f>IF(OR(A51="",$H$4=""),"",IF(ISNUMBER(F51),"Turned in",IF(UPPER(F51)="EX","Excused",IF(OR(UPPER(F51)="M",Assignments!I42=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A51="",$H$4=""),"",IF(ISNUMBER(F51),"Submitted",IF(UPPER(F51)="EX","Excused",IF(OR(UPPER(F51)="M",Assignments!I42=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18135,7 +18149,7 @@
         <v/>
       </c>
       <c r="H52" s="70">
-        <f>IF(OR(A52="",$H$4=""),"",IF(ISNUMBER(F52),"Turned in",IF(UPPER(F52)="EX","Excused",IF(OR(UPPER(F52)="M",Assignments!I43=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A52="",$H$4=""),"",IF(ISNUMBER(F52),"Submitted",IF(UPPER(F52)="EX","Excused",IF(OR(UPPER(F52)="M",Assignments!I43=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18169,7 +18183,7 @@
         <v/>
       </c>
       <c r="H53" s="70">
-        <f>IF(OR(A53="",$H$4=""),"",IF(ISNUMBER(F53),"Turned in",IF(UPPER(F53)="EX","Excused",IF(OR(UPPER(F53)="M",Assignments!I44=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A53="",$H$4=""),"",IF(ISNUMBER(F53),"Submitted",IF(UPPER(F53)="EX","Excused",IF(OR(UPPER(F53)="M",Assignments!I44=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18203,7 +18217,7 @@
         <v/>
       </c>
       <c r="H54" s="70">
-        <f>IF(OR(A54="",$H$4=""),"",IF(ISNUMBER(F54),"Turned in",IF(UPPER(F54)="EX","Excused",IF(OR(UPPER(F54)="M",Assignments!I45=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A54="",$H$4=""),"",IF(ISNUMBER(F54),"Submitted",IF(UPPER(F54)="EX","Excused",IF(OR(UPPER(F54)="M",Assignments!I45=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18237,7 +18251,7 @@
         <v/>
       </c>
       <c r="H55" s="70">
-        <f>IF(OR(A55="",$H$4=""),"",IF(ISNUMBER(F55),"Turned in",IF(UPPER(F55)="EX","Excused",IF(OR(UPPER(F55)="M",Assignments!I46=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A55="",$H$4=""),"",IF(ISNUMBER(F55),"Submitted",IF(UPPER(F55)="EX","Excused",IF(OR(UPPER(F55)="M",Assignments!I46=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18271,7 +18285,7 @@
         <v/>
       </c>
       <c r="H56" s="70">
-        <f>IF(OR(A56="",$H$4=""),"",IF(ISNUMBER(F56),"Turned in",IF(UPPER(F56)="EX","Excused",IF(OR(UPPER(F56)="M",Assignments!I47=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A56="",$H$4=""),"",IF(ISNUMBER(F56),"Submitted",IF(UPPER(F56)="EX","Excused",IF(OR(UPPER(F56)="M",Assignments!I47=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18305,7 +18319,7 @@
         <v/>
       </c>
       <c r="H57" s="70">
-        <f>IF(OR(A57="",$H$4=""),"",IF(ISNUMBER(F57),"Turned in",IF(UPPER(F57)="EX","Excused",IF(OR(UPPER(F57)="M",Assignments!I48=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A57="",$H$4=""),"",IF(ISNUMBER(F57),"Submitted",IF(UPPER(F57)="EX","Excused",IF(OR(UPPER(F57)="M",Assignments!I48=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18339,7 +18353,7 @@
         <v/>
       </c>
       <c r="H58" s="70">
-        <f>IF(OR(A58="",$H$4=""),"",IF(ISNUMBER(F58),"Turned in",IF(UPPER(F58)="EX","Excused",IF(OR(UPPER(F58)="M",Assignments!I49=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A58="",$H$4=""),"",IF(ISNUMBER(F58),"Submitted",IF(UPPER(F58)="EX","Excused",IF(OR(UPPER(F58)="M",Assignments!I49=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18373,7 +18387,7 @@
         <v/>
       </c>
       <c r="H59" s="70">
-        <f>IF(OR(A59="",$H$4=""),"",IF(ISNUMBER(F59),"Turned in",IF(UPPER(F59)="EX","Excused",IF(OR(UPPER(F59)="M",Assignments!I50=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A59="",$H$4=""),"",IF(ISNUMBER(F59),"Submitted",IF(UPPER(F59)="EX","Excused",IF(OR(UPPER(F59)="M",Assignments!I50=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18407,7 +18421,7 @@
         <v/>
       </c>
       <c r="H60" s="70">
-        <f>IF(OR(A60="",$H$4=""),"",IF(ISNUMBER(F60),"Turned in",IF(UPPER(F60)="EX","Excused",IF(OR(UPPER(F60)="M",Assignments!I51=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A60="",$H$4=""),"",IF(ISNUMBER(F60),"Submitted",IF(UPPER(F60)="EX","Excused",IF(OR(UPPER(F60)="M",Assignments!I51=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18441,7 +18455,7 @@
         <v/>
       </c>
       <c r="H61" s="70">
-        <f>IF(OR(A61="",$H$4=""),"",IF(ISNUMBER(F61),"Turned in",IF(UPPER(F61)="EX","Excused",IF(OR(UPPER(F61)="M",Assignments!I52=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A61="",$H$4=""),"",IF(ISNUMBER(F61),"Submitted",IF(UPPER(F61)="EX","Excused",IF(OR(UPPER(F61)="M",Assignments!I52=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18475,7 +18489,7 @@
         <v/>
       </c>
       <c r="H62" s="70">
-        <f>IF(OR(A62="",$H$4=""),"",IF(ISNUMBER(F62),"Turned in",IF(UPPER(F62)="EX","Excused",IF(OR(UPPER(F62)="M",Assignments!I53=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A62="",$H$4=""),"",IF(ISNUMBER(F62),"Submitted",IF(UPPER(F62)="EX","Excused",IF(OR(UPPER(F62)="M",Assignments!I53=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18509,7 +18523,7 @@
         <v/>
       </c>
       <c r="H63" s="70">
-        <f>IF(OR(A63="",$H$4=""),"",IF(ISNUMBER(F63),"Turned in",IF(UPPER(F63)="EX","Excused",IF(OR(UPPER(F63)="M",Assignments!I54=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A63="",$H$4=""),"",IF(ISNUMBER(F63),"Submitted",IF(UPPER(F63)="EX","Excused",IF(OR(UPPER(F63)="M",Assignments!I54=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18543,7 +18557,7 @@
         <v/>
       </c>
       <c r="H64" s="70">
-        <f>IF(OR(A64="",$H$4=""),"",IF(ISNUMBER(F64),"Turned in",IF(UPPER(F64)="EX","Excused",IF(OR(UPPER(F64)="M",Assignments!I55=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A64="",$H$4=""),"",IF(ISNUMBER(F64),"Submitted",IF(UPPER(F64)="EX","Excused",IF(OR(UPPER(F64)="M",Assignments!I55=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18577,7 +18591,7 @@
         <v/>
       </c>
       <c r="H65" s="70">
-        <f>IF(OR(A65="",$H$4=""),"",IF(ISNUMBER(F65),"Turned in",IF(UPPER(F65)="EX","Excused",IF(OR(UPPER(F65)="M",Assignments!I56=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A65="",$H$4=""),"",IF(ISNUMBER(F65),"Submitted",IF(UPPER(F65)="EX","Excused",IF(OR(UPPER(F65)="M",Assignments!I56=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18611,7 +18625,7 @@
         <v/>
       </c>
       <c r="H66" s="70">
-        <f>IF(OR(A66="",$H$4=""),"",IF(ISNUMBER(F66),"Turned in",IF(UPPER(F66)="EX","Excused",IF(OR(UPPER(F66)="M",Assignments!I57=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A66="",$H$4=""),"",IF(ISNUMBER(F66),"Submitted",IF(UPPER(F66)="EX","Excused",IF(OR(UPPER(F66)="M",Assignments!I57=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18645,7 +18659,7 @@
         <v/>
       </c>
       <c r="H67" s="70">
-        <f>IF(OR(A67="",$H$4=""),"",IF(ISNUMBER(F67),"Turned in",IF(UPPER(F67)="EX","Excused",IF(OR(UPPER(F67)="M",Assignments!I58=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A67="",$H$4=""),"",IF(ISNUMBER(F67),"Submitted",IF(UPPER(F67)="EX","Excused",IF(OR(UPPER(F67)="M",Assignments!I58=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18679,7 +18693,7 @@
         <v/>
       </c>
       <c r="H68" s="70">
-        <f>IF(OR(A68="",$H$4=""),"",IF(ISNUMBER(F68),"Turned in",IF(UPPER(F68)="EX","Excused",IF(OR(UPPER(F68)="M",Assignments!I59=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A68="",$H$4=""),"",IF(ISNUMBER(F68),"Submitted",IF(UPPER(F68)="EX","Excused",IF(OR(UPPER(F68)="M",Assignments!I59=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18713,7 +18727,7 @@
         <v/>
       </c>
       <c r="H69" s="70">
-        <f>IF(OR(A69="",$H$4=""),"",IF(ISNUMBER(F69),"Turned in",IF(UPPER(F69)="EX","Excused",IF(OR(UPPER(F69)="M",Assignments!I60=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A69="",$H$4=""),"",IF(ISNUMBER(F69),"Submitted",IF(UPPER(F69)="EX","Excused",IF(OR(UPPER(F69)="M",Assignments!I60=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18747,7 +18761,7 @@
         <v/>
       </c>
       <c r="H70" s="70">
-        <f>IF(OR(A70="",$H$4=""),"",IF(ISNUMBER(F70),"Turned in",IF(UPPER(F70)="EX","Excused",IF(OR(UPPER(F70)="M",Assignments!I61=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A70="",$H$4=""),"",IF(ISNUMBER(F70),"Submitted",IF(UPPER(F70)="EX","Excused",IF(OR(UPPER(F70)="M",Assignments!I61=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18781,7 +18795,7 @@
         <v/>
       </c>
       <c r="H71" s="70">
-        <f>IF(OR(A71="",$H$4=""),"",IF(ISNUMBER(F71),"Turned in",IF(UPPER(F71)="EX","Excused",IF(OR(UPPER(F71)="M",Assignments!I62=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A71="",$H$4=""),"",IF(ISNUMBER(F71),"Submitted",IF(UPPER(F71)="EX","Excused",IF(OR(UPPER(F71)="M",Assignments!I62=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18815,7 +18829,7 @@
         <v/>
       </c>
       <c r="H72" s="70">
-        <f>IF(OR(A72="",$H$4=""),"",IF(ISNUMBER(F72),"Turned in",IF(UPPER(F72)="EX","Excused",IF(OR(UPPER(F72)="M",Assignments!I63=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A72="",$H$4=""),"",IF(ISNUMBER(F72),"Submitted",IF(UPPER(F72)="EX","Excused",IF(OR(UPPER(F72)="M",Assignments!I63=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18849,7 +18863,7 @@
         <v/>
       </c>
       <c r="H73" s="70">
-        <f>IF(OR(A73="",$H$4=""),"",IF(ISNUMBER(F73),"Turned in",IF(UPPER(F73)="EX","Excused",IF(OR(UPPER(F73)="M",Assignments!I64=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A73="",$H$4=""),"",IF(ISNUMBER(F73),"Submitted",IF(UPPER(F73)="EX","Excused",IF(OR(UPPER(F73)="M",Assignments!I64=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
@@ -18883,7 +18897,7 @@
         <v/>
       </c>
       <c r="H74" s="70">
-        <f>IF(OR(A74="",$H$4=""),"",IF(ISNUMBER(F74),"Turned in",IF(UPPER(F74)="EX","Excused",IF(OR(UPPER(F74)="M",Assignments!I65=1),"Missing","Not due yet"))))</f>
+        <f>IF(OR(A74="",$H$4=""),"",IF(ISNUMBER(F74),"Submitted",IF(UPPER(F74)="EX","Excused",IF(OR(UPPER(F74)="M",Assignments!I65=1),"Missing","Not due yet"))))</f>
         <v/>
       </c>
     </row>
